--- a/order_generation/PO_import_filled/PO_import_test1.xlsx
+++ b/order_generation/PO_import_filled/PO_import_test1.xlsx
@@ -898,7 +898,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Elasticbrush01</t>
+          <t>EEHB-NBB</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -907,16 +907,18 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.85</v>
+        <v>12.89</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>梳身半降解材料（用新材料防断裂）加麦秸秆5645 C绿色，尼龙丝0.8mm7529U灰色尼龙丝颜色同beter，棕色 ecoed logo颜色同beter！染头颜色同梳体. 包装方式：白卡盒，卡盒我司供，箱规120/24</t>
+          <t>手柄表面电镀处理尽量光亮，黑色手柄做防静电处理。
+气垫颜色（打样确认色），植猪鬃毛，梳针颜色黑色防静电，植0.8 mm细尼龙针染头和梳针颜色一致，染头尽量偏小（视觉效果染头和梳针一体）梳针做防静电处理。
+LOGO：ellen evyse 颜色印金</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -924,17 +926,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test1-2</t>
+          <t>test1-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>宁波瑾秀制刷科技有限公司</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -976,7 +978,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>EC221-1-1</t>
+          <t>EEHB-NBB-4</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -985,31 +987,331 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>鱼骨梳包装，350g白卡双面印刷，FSC 绿色</t>
+          <t>清洁刷，注塑体黑色，植毛黑色尼龙毛，0.7mm直径，长度25mm，定制Norsewood滑块logo，产品做哑光，logo处做亮光。需打样再做货</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test1-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>义乌市一柠饰品有限公司</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-1C</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>浅咖色</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test1-2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>义乌市一柠饰品有限公司</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-1B</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test1-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>盐城市艳丽工艺品有限公司</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-2</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>12*25黑色棘皮绒单面，黑色棉绳，烫金logo</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test1-4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>XX印刷厂</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-3</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>猪鬃红色胶皮天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
